--- a/extensions/impix/확장정의서.xlsx
+++ b/extensions/impix/확장정의서.xlsx
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1126,15 +1126,15 @@
         </is>
       </c>
       <c r="M2" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F2)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F2)</f>
         <v/>
       </c>
       <c r="N2" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F2,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F2,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O2" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F2,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F2,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -1216,15 +1216,15 @@
       </c>
       <c r="L3" s="7" t="n"/>
       <c r="M3" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F3)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F3)</f>
         <v/>
       </c>
       <c r="N3" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F3,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F3,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O3" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F3,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F3,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -1310,15 +1310,15 @@
         </is>
       </c>
       <c r="M4" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F4)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F4)</f>
         <v/>
       </c>
       <c r="N4" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F4,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F4,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O4" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F4,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F4,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P4" s="7" t="inlineStr">
@@ -1404,15 +1404,15 @@
         </is>
       </c>
       <c r="M5" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F5)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F5)</f>
         <v/>
       </c>
       <c r="N5" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F5,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F5,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O5" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F5,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F5,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P5" s="7" t="inlineStr">
@@ -1498,15 +1498,15 @@
         </is>
       </c>
       <c r="M6" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F6)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F6)</f>
         <v/>
       </c>
       <c r="N6" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F6,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F6,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O6" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F6,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F6,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -1588,15 +1588,15 @@
       </c>
       <c r="L7" s="7" t="n"/>
       <c r="M7" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F7)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F7)</f>
         <v/>
       </c>
       <c r="N7" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F7,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F7,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O7" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F7,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F7,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P7" s="7" t="inlineStr">
@@ -1682,15 +1682,15 @@
       </c>
       <c r="L8" s="7" t="n"/>
       <c r="M8" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F8)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F8)</f>
         <v/>
       </c>
       <c r="N8" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F8,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F8,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O8" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F8,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F8,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -1776,15 +1776,15 @@
       </c>
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F9)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F9)</f>
         <v/>
       </c>
       <c r="N9" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F9,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F9,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O9" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F9,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F9,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P9" s="7" t="inlineStr">
@@ -1870,15 +1870,15 @@
       </c>
       <c r="L10" s="7" t="n"/>
       <c r="M10" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F10)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F10)</f>
         <v/>
       </c>
       <c r="N10" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F10,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F10,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O10" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F10,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F10,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -1964,15 +1964,15 @@
       </c>
       <c r="L11" s="7" t="n"/>
       <c r="M11" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F11)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F11)</f>
         <v/>
       </c>
       <c r="N11" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F11,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F11,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O11" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F11,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F11,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P11" s="7" t="inlineStr">
@@ -2058,15 +2058,15 @@
       </c>
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F12)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F12)</f>
         <v/>
       </c>
       <c r="N12" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F12,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F12,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O12" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F12,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F12,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -2152,15 +2152,15 @@
       </c>
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F13)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F13)</f>
         <v/>
       </c>
       <c r="N13" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F13,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F13,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O13" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F13,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F13,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P13" s="7" t="inlineStr">
@@ -2246,15 +2246,15 @@
       </c>
       <c r="L14" s="7" t="n"/>
       <c r="M14" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F14)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F14)</f>
         <v/>
       </c>
       <c r="N14" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F14,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F14,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O14" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F14,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F14,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -2340,15 +2340,15 @@
       </c>
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F15)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F15)</f>
         <v/>
       </c>
       <c r="N15" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F15,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F15,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O15" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F15,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F15,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -2434,15 +2434,15 @@
       </c>
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F16)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F16)</f>
         <v/>
       </c>
       <c r="N16" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F16,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F16,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O16" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F16,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F16,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -2528,15 +2528,15 @@
       </c>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F17)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F17)</f>
         <v/>
       </c>
       <c r="N17" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F17,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F17,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O17" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F17,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F17,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P17" s="7" t="inlineStr">
@@ -2622,15 +2622,15 @@
       </c>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F18)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F18)</f>
         <v/>
       </c>
       <c r="N18" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F18,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F18,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O18" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F18,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F18,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P18" s="7" t="inlineStr">
@@ -2716,15 +2716,15 @@
       </c>
       <c r="L19" s="7" t="n"/>
       <c r="M19" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F19)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F19)</f>
         <v/>
       </c>
       <c r="N19" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F19,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F19,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O19" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F19,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F19,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -2810,15 +2810,15 @@
       </c>
       <c r="L20" s="7" t="n"/>
       <c r="M20" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F20)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F20)</f>
         <v/>
       </c>
       <c r="N20" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F20,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F20,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O20" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F20,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F20,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -2904,15 +2904,15 @@
       </c>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F21)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F21)</f>
         <v/>
       </c>
       <c r="N21" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F21,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F21,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O21" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F21,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F21,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P21" s="7" t="inlineStr">
@@ -2998,15 +2998,15 @@
       </c>
       <c r="L22" s="7" t="n"/>
       <c r="M22" s="7">
-        <f>COUNTIF(테이블정의서!$A$2:$A$191,F22)</f>
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F22)</f>
         <v/>
       </c>
       <c r="N22" s="7">
-        <f>COUNTIFS(테이블정의서!$A$2:$A$191,F22,테이블정의서!$H$2:$H$191,"기본")</f>
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F22,테이블정의서!$H$2:$H$197,"기본")</f>
         <v/>
       </c>
       <c r="O22" s="7">
-        <f>COUNTIFS(관계목록!$B$2:$B$62,F22,관계목록!$H$2:$H$62,"물리")</f>
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F22,관계목록!$H$2:$H$64,"물리")</f>
         <v/>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -3035,6 +3035,100 @@
         </is>
       </c>
       <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>생산관리</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>로트 확장</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>로트에 출처(생산·구매·이관)와 공급사·공급사 LOT 번호를 더한다. 구매 자재 LOT와 MES 도입 전 LOT를 표준 로트로 등록해 계보를 자재 단계까지 잇는다.</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>LotExtSequenceNo</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>EnterpriseID + LotID</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Core UK</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7">
+        <f>COUNTIF(테이블정의서!$A$2:$A$197,F23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="7">
+        <f>COUNTIFS(테이블정의서!$A$2:$A$197,F23,테이블정의서!$H$2:$H$197,"기본")</f>
+        <v/>
+      </c>
+      <c r="O23" s="7">
+        <f>COUNTIFS(관계목록!$B$2:$B$64,F23,관계목록!$H$2:$H$64,"물리")</f>
+        <v/>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>확장 속성</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr">
+        <is>
+          <t>② 확장 속성</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>mes.tb_lot, erp.tb_mm_gr, erp.tb_mm_stock_lot, erp.tb_sd_dlv</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>SC05·SC06 / QM09 / Q-SC05-01·Q-SC06-14</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -3062,7 +3156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U191"/>
+  <dimension ref="A1:U197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -19177,6 +19271,525 @@
       </c>
       <c r="T191" s="7" t="n"/>
       <c r="U191" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>로트 확장</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" s="8" t="inlineStr">
+        <is>
+          <t>로트 확장 일련번호</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="inlineStr">
+        <is>
+          <t>LotExtSequenceNo</t>
+        </is>
+      </c>
+      <c r="G192" s="8" t="inlineStr">
+        <is>
+          <t>LotExtSequenceNo</t>
+        </is>
+      </c>
+      <c r="H192" s="8" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="I192" s="8" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="J192" s="8" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="K192" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L192" s="8" t="n"/>
+      <c r="M192" s="8" t="n"/>
+      <c r="N192" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O192" s="8" t="n"/>
+      <c r="P192" s="8" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
+      <c r="Q192" s="8" t="n"/>
+      <c r="R192" s="8" t="inlineStr">
+        <is>
+          <t>— 테이블 행을 식별하는 일련번호(PK, 대리키) — 표준 외 물리 컬럼
+— 자동 증가 값(IDENTITY)으로 부여하며 다른 테이블이 참조하지 않음(FK는 UK 참조)</t>
+        </is>
+      </c>
+      <c r="S192" s="8" t="n"/>
+      <c r="T192" s="8" t="n"/>
+      <c r="U192" s="8" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>로트 확장</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>회사식별자</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>EnterpriseID</t>
+        </is>
+      </c>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t>EnterpriseID</t>
+        </is>
+      </c>
+      <c r="H193" s="8" t="inlineStr">
+        <is>
+          <t>Core키</t>
+        </is>
+      </c>
+      <c r="I193" s="8" t="inlineStr">
+        <is>
+          <t>IDREF</t>
+        </is>
+      </c>
+      <c r="J193" s="8" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="K193" s="8" t="n"/>
+      <c r="L193" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="M193" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N193" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O193" s="8" t="inlineStr">
+        <is>
+          <t>Lot.EnterpriseID</t>
+        </is>
+      </c>
+      <c r="P193" s="8" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="Q193" s="8" t="n"/>
+      <c r="R193" s="8" t="inlineStr">
+        <is>
+          <t>— 확장 대상 Core 명사 로트(Lot)의 식별 키(UK) — 1:1 확장
+— 참조 대상: 로트(Lot)</t>
+        </is>
+      </c>
+      <c r="S193" s="8" t="n"/>
+      <c r="T193" s="8" t="n"/>
+      <c r="U193" s="8" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>로트 확장</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>로트식별자</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>LotID</t>
+        </is>
+      </c>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t>LotID</t>
+        </is>
+      </c>
+      <c r="H194" s="8" t="inlineStr">
+        <is>
+          <t>Core키</t>
+        </is>
+      </c>
+      <c r="I194" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="J194" s="8" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="K194" s="8" t="n"/>
+      <c r="L194" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="M194" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N194" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O194" s="8" t="inlineStr">
+        <is>
+          <t>Lot.LotID</t>
+        </is>
+      </c>
+      <c r="P194" s="8" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="Q194" s="8" t="n"/>
+      <c r="R194" s="8" t="inlineStr">
+        <is>
+          <t>— 확장 대상 Core 명사 로트(Lot)의 식별 키(UK) — 1:1 확장
+— 참조 대상: 로트(Lot)</t>
+        </is>
+      </c>
+      <c r="S194" s="8" t="n"/>
+      <c r="T194" s="8" t="n"/>
+      <c r="U194" s="8" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>로트 확장</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>로트출처유형</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>LotOriginType</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>LotOriginType</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="I195" s="7" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="J195" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="K195" s="7" t="n"/>
+      <c r="L195" s="7" t="n"/>
+      <c r="M195" s="7" t="n"/>
+      <c r="N195" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O195" s="7" t="n"/>
+      <c r="P195" s="7" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="Q195" s="7" t="inlineStr">
+        <is>
+          <t>CommonCodeGroup=LotOriginType</t>
+        </is>
+      </c>
+      <c r="R195" s="7" t="inlineStr">
+        <is>
+          <t>— 로트가 만들어진 출처: 생산(MES)·구매(입고)·이관(MES 도입 전·기초 재고)
+— 참조 대상: 공통코드정보(CommonCodeMaster)의 코드</t>
+        </is>
+      </c>
+      <c r="S195" s="7" t="inlineStr">
+        <is>
+          <t>(명세별 상수)</t>
+        </is>
+      </c>
+      <c r="T195" s="7" t="inlineStr">
+        <is>
+          <t>표준 LotType은 고정형(양산·개발 등) — 구매·이관 LOT 구분 불가</t>
+        </is>
+      </c>
+      <c r="U195" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>로트 확장</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>공급사식별자</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>VendorID</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>VendorID</t>
+        </is>
+      </c>
+      <c r="H196" s="7" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="inlineStr">
+        <is>
+          <t>IDREF</t>
+        </is>
+      </c>
+      <c r="J196" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(50)</t>
+        </is>
+      </c>
+      <c r="K196" s="7" t="n"/>
+      <c r="L196" s="7" t="n"/>
+      <c r="M196" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N196" s="7" t="n"/>
+      <c r="O196" s="7" t="inlineStr">
+        <is>
+          <t>VendorPartyMaster.VendorID</t>
+        </is>
+      </c>
+      <c r="P196" s="7" t="inlineStr">
+        <is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="Q196" s="7" t="n"/>
+      <c r="R196" s="7" t="inlineStr">
+        <is>
+          <t>— 구매 LOT의 공급사
+— 참조 대상: 공급사(VendorPartyMaster)</t>
+        </is>
+      </c>
+      <c r="S196" s="7" t="inlineStr">
+        <is>
+          <t>erp.tb_mm_gr.vend_cd</t>
+        </is>
+      </c>
+      <c r="T196" s="7" t="n"/>
+      <c r="U196" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>로트 확장</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>공급사로트번호</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>VendorLotNumber</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>VendorLotNumber</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>확장</t>
+        </is>
+      </c>
+      <c r="I197" s="7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J197" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="K197" s="7" t="n"/>
+      <c r="L197" s="7" t="n"/>
+      <c r="M197" s="7" t="n"/>
+      <c r="N197" s="7" t="n"/>
+      <c r="O197" s="7" t="n"/>
+      <c r="P197" s="7" t="inlineStr">
+        <is>
+          <t>비대상</t>
+        </is>
+      </c>
+      <c r="Q197" s="7" t="n"/>
+      <c r="R197" s="7" t="inlineStr">
+        <is>
+          <t>— 공급사가 붙인 원래 LOT 번호. 공급사 LOT 번호는 품목 간에 겹치므로 로트식별자는 '공급사LOT_품목'으로 만든다</t>
+        </is>
+      </c>
+      <c r="S197" s="7" t="inlineStr">
+        <is>
+          <t>erp.tb_mm_gr.vend_lot</t>
+        </is>
+      </c>
+      <c r="T197" s="7" t="inlineStr">
+        <is>
+          <t>Q-SC06-14 공급사 LOT 역추적</t>
+        </is>
+      </c>
+      <c r="U197" s="7" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -19219,7 +19832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -21534,6 +22147,82 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>EnterpriseID, LotID</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>EnterpriseID, LotID</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>확장 대상(1:1)</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Core 행 1개당 확장 행 최대 1개</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>물리</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>EnterpriseID, VendorID</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>VendorPartyMaster</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>EnterpriseID, VendorID</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>명사 참조</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>물리</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21545,7 +22234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -22046,12 +22735,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>ProductionOrderStatusCode</t>
+          <t>LotOriginType</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>생산지시상태코드</t>
+          <t>로트출처유형</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -22062,17 +22751,17 @@
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>생산지시 진행 상태</t>
+          <t>로트 출처</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>ProductionOrderStatusCode</t>
+          <t>LotOriginType</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>ProductionOrder(확장)</t>
+          <t>Lot(확장)</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -22097,12 +22786,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>AlarmSeverityCode</t>
+          <t>ProductionOrderStatusCode</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>알람중요도코드</t>
+          <t>생산지시상태코드</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -22113,17 +22802,17 @@
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>알람 중요도</t>
+          <t>생산지시 진행 상태</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>AlarmSeverityCode</t>
+          <t>ProductionOrderStatusCode</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Alarm(확장)</t>
+          <t>ProductionOrder(확장)</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -22143,38 +22832,38 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>판매관리(확장)</t>
+          <t>생산관리(확장)</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>CustomerGroupCode</t>
+          <t>AlarmSeverityCode</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>고객군코드</t>
+          <t>알람중요도코드</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>회사정의</t>
+          <t>고정형</t>
         </is>
       </c>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>고객군</t>
+          <t>알람 중요도</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>CustomerGroupCode</t>
+          <t>AlarmSeverityCode</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>CustomerPartyMaster(확장)</t>
+          <t>Alarm(확장)</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -22194,43 +22883,43 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>생산관리</t>
+          <t>판매관리(확장)</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>EquipmentErrorCode</t>
+          <t>CustomerGroupCode</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>설비오류코드</t>
+          <t>고객군코드</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>회사정의(접두어 EQ-)</t>
+          <t>회사정의</t>
         </is>
       </c>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>표준 그룹에 회사 코드 추가</t>
+          <t>고객군</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>ErrorCode</t>
+          <t>CustomerGroupCode</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>EquipmentState·Alarm</t>
+          <t>CustomerPartyMaster(확장)</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>표준 그룹 하위 확장</t>
+          <t>신규 그룹</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -22245,22 +22934,22 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>기준정보</t>
+          <t>생산관리</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>ItemLargeClass</t>
+          <t>EquipmentErrorCode</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>품목대분류</t>
+          <t>설비오류코드</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>회사정의(계층)</t>
+          <t>회사정의(접두어 EQ-)</t>
         </is>
       </c>
       <c r="F14" s="7" t="n"/>
@@ -22271,12 +22960,12 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>ItemLargeClass</t>
+          <t>ErrorCode</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>ItemMaster</t>
+          <t>EquipmentState·Alarm</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -22301,12 +22990,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>EquipmentLargeClass</t>
+          <t>ItemLargeClass</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>설비대분류</t>
+          <t>품목대분류</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -22322,20 +23011,71 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
+          <t>ItemLargeClass</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>ItemMaster</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>표준 그룹 하위 확장</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>기준정보</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
           <t>EquipmentLargeClass</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>설비대분류</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>회사정의(계층)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>표준 그룹에 회사 코드 추가</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>EquipmentLargeClass</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>표준 그룹 하위 확장</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -22360,7 +23100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -24966,27 +25706,27 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>ProductionOrderStatusCode</t>
+          <t>LotOriginType</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>생산지시상태코드</t>
+          <t>로트출처유형</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>PLANNED</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Production</t>
         </is>
       </c>
       <c r="H35" s="7" t="n">
@@ -25012,12 +25752,12 @@
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>MES</t>
         </is>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>계획</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="Q35" s="7" t="n"/>
@@ -25038,27 +25778,27 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>ProductionOrderStatusCode</t>
+          <t>LotOriginType</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>생산지시상태코드</t>
+          <t>로트출처유형</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>RELEASED</t>
+          <t>PURCHASE</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Released</t>
+          <t>Purchase</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -25084,12 +25824,12 @@
       </c>
       <c r="O36" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="Q36" s="7" t="n"/>
@@ -25110,27 +25850,27 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>ProductionOrderStatusCode</t>
+          <t>LotOriginType</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>생산지시상태코드</t>
+          <t>로트출처유형</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>LEGACY</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>이관</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Legacy</t>
         </is>
       </c>
       <c r="H37" s="7" t="n">
@@ -25156,12 +25896,12 @@
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>HIST</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>이관</t>
         </is>
       </c>
       <c r="Q37" s="7" t="n"/>
@@ -25192,21 +25932,21 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>PLANNED</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>계획</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="H38" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
@@ -25228,12 +25968,12 @@
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>계획</t>
         </is>
       </c>
       <c r="Q38" s="7" t="n"/>
@@ -25264,21 +26004,21 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>RELEASED</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>Released</t>
         </is>
       </c>
       <c r="H39" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -25300,12 +26040,12 @@
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="Q39" s="7" t="n"/>
@@ -25326,31 +26066,31 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>AlarmSeverityCode</t>
+          <t>ProductionOrderStatusCode</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>알람중요도코드</t>
+          <t>생산지시상태코드</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="H40" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
@@ -25372,12 +26112,12 @@
       </c>
       <c r="O40" s="7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="Q40" s="7" t="n"/>
@@ -25398,31 +26138,31 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>AlarmSeverityCode</t>
+          <t>ProductionOrderStatusCode</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>알람중요도코드</t>
+          <t>생산지시상태코드</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="H41" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
@@ -25444,12 +26184,12 @@
       </c>
       <c r="O41" s="7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="Q41" s="7" t="n"/>
@@ -25470,31 +26210,31 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>AlarmSeverityCode</t>
+          <t>ProductionOrderStatusCode</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>알람중요도코드</t>
+          <t>생산지시상태코드</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="H42" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
@@ -25516,12 +26256,12 @@
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="Q42" s="7" t="n"/>
@@ -25537,32 +26277,32 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>판매관리(확장)</t>
+          <t>생산관리(확장)</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>CustomerGroupCode</t>
+          <t>AlarmSeverityCode</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>고객군코드</t>
+          <t>알람중요도코드</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>완성차</t>
+          <t>상</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>OEM</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H43" s="7" t="n">
@@ -25588,12 +26328,12 @@
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>H</t>
         </is>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>완성차</t>
+          <t>상</t>
         </is>
       </c>
       <c r="Q43" s="7" t="n"/>
@@ -25609,32 +26349,32 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>판매관리(확장)</t>
+          <t>생산관리(확장)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>CustomerGroupCode</t>
+          <t>AlarmSeverityCode</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>고객군코드</t>
+          <t>알람중요도코드</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>보수용</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>Aftermarket</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H44" s="7" t="n">
@@ -25660,12 +26400,12 @@
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>M</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>보수용</t>
+          <t>중</t>
         </is>
       </c>
       <c r="Q44" s="7" t="n"/>
@@ -25681,36 +26421,36 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>생산관리</t>
+          <t>생산관리(확장)</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>EquipmentErrorCode</t>
+          <t>AlarmSeverityCode</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>설비오류코드</t>
+          <t>알람중요도코드</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>진동 과다</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Excessive vibration</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H45" s="7" t="n">
-        <v>108</v>
+        <v>3</v>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
@@ -25719,14 +26459,10 @@
       </c>
       <c r="J45" s="7" t="n"/>
       <c r="K45" s="7" t="n"/>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>가공 설비 진동 과다(공구 마모 징후)</t>
-        </is>
-      </c>
+      <c r="L45" s="7" t="n"/>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>표준 그룹 하위 확장</t>
+          <t>확장</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
@@ -25736,12 +26472,12 @@
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>A202</t>
+          <t>L</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>진동 과다</t>
+          <t>하</t>
         </is>
       </c>
       <c r="Q45" s="7" t="n"/>
@@ -25757,36 +26493,36 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>기준정보</t>
+          <t>판매관리(확장)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>ItemLargeClass</t>
+          <t>CustomerGroupCode</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>품목대분류</t>
+          <t>고객군코드</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>CSM</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>소모품</t>
+          <t>완성차</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Consumables</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="H46" s="7" t="n">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
@@ -25795,14 +26531,10 @@
       </c>
       <c r="J46" s="7" t="n"/>
       <c r="K46" s="7" t="n"/>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>냉각수·이형제 등 소모성 자재</t>
-        </is>
-      </c>
+      <c r="L46" s="7" t="n"/>
       <c r="M46" s="7" t="inlineStr">
         <is>
-          <t>표준 그룹 하위 확장</t>
+          <t>확장</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
@@ -25812,12 +26544,12 @@
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>CSM</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>소모품</t>
+          <t>완성차</t>
         </is>
       </c>
       <c r="Q46" s="7" t="n"/>
@@ -25833,36 +26565,36 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>기준정보</t>
+          <t>판매관리(확장)</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>EquipmentLargeClass</t>
+          <t>CustomerGroupCode</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>설비대분류</t>
+          <t>고객군코드</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>CST</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>주조기</t>
+          <t>보수용</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>Casting machine</t>
+          <t>Aftermarket</t>
         </is>
       </c>
       <c r="H47" s="7" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
@@ -25874,7 +26606,7 @@
       <c r="L47" s="7" t="n"/>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>표준 그룹 하위 확장</t>
+          <t>확장</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
@@ -25884,12 +26616,12 @@
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>DCM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>주조기</t>
+          <t>보수용</t>
         </is>
       </c>
       <c r="Q47" s="7" t="n"/>
@@ -25905,36 +26637,36 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>기준정보</t>
+          <t>생산관리</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>EquipmentLargeClass</t>
+          <t>EquipmentErrorCode</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>설비대분류</t>
+          <t>설비오류코드</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>CLN</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>세척기</t>
+          <t>진동 과다</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>Washer</t>
+          <t>Excessive vibration</t>
         </is>
       </c>
       <c r="H48" s="7" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
@@ -25943,7 +26675,11 @@
       </c>
       <c r="J48" s="7" t="n"/>
       <c r="K48" s="7" t="n"/>
-      <c r="L48" s="7" t="n"/>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>가공 설비 진동 과다(공구 마모 징후)</t>
+        </is>
+      </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
           <t>표준 그룹 하위 확장</t>
@@ -25956,12 +26692,12 @@
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>A202</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>세척기</t>
+          <t>진동 과다</t>
         </is>
       </c>
       <c r="Q48" s="7" t="n"/>
@@ -25982,31 +26718,31 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>EquipmentLargeClass</t>
+          <t>ItemLargeClass</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>설비대분류</t>
+          <t>품목대분류</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>CSM</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>조립기</t>
+          <t>소모품</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>Assembly machine</t>
+          <t>Consumables</t>
         </is>
       </c>
       <c r="H49" s="7" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
@@ -26015,7 +26751,11 @@
       </c>
       <c r="J49" s="7" t="n"/>
       <c r="K49" s="7" t="n"/>
-      <c r="L49" s="7" t="n"/>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>냉각수·이형제 등 소모성 자재</t>
+        </is>
+      </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
           <t>표준 그룹 하위 확장</t>
@@ -26028,12 +26768,12 @@
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>CSM</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>조립기</t>
+          <t>소모품</t>
         </is>
       </c>
       <c r="Q49" s="7" t="n"/>
@@ -26064,21 +26804,21 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>PKM</t>
+          <t>CST</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>포장기</t>
+          <t>주조기</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>Packing machine</t>
+          <t>Casting machine</t>
         </is>
       </c>
       <c r="H50" s="7" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
@@ -26100,16 +26840,232 @@
       </c>
       <c r="O50" s="7" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>DCM</t>
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>포장기</t>
+          <t>주조기</t>
         </is>
       </c>
       <c r="Q50" s="7" t="n"/>
       <c r="R50" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>기준정보</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>EquipmentLargeClass</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>설비대분류</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>CLN</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>세척기</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Washer</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>표준 그룹 하위 확장</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>세척기</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="n"/>
+      <c r="R51" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>기준정보</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>EquipmentLargeClass</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>설비대분류</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>조립기</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Assembly machine</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>103</v>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="n"/>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="7" t="n"/>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>표준 그룹 하위 확장</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>조립기</t>
+        </is>
+      </c>
+      <c r="Q52" s="7" t="n"/>
+      <c r="R52" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>기준정보</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>EquipmentLargeClass</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>설비대분류</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>PKM</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>포장기</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Packing machine</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>표준 그룹 하위 확장</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>PKG</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>포장기</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="n"/>
+      <c r="R53" s="7" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -26137,7 +27093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27869,17 +28825,17 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>SC04 / Q-SC04-17</t>
+          <t>SC05·SC06</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>mes.tb_alarm.alm_lvl</t>
+          <t>erp.tb_mm_gr.vend_lot (+item_cd)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>알람 중요도 H/M/L</t>
+          <t>공급사 LOT</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -27889,12 +28845,12 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>AlarmExt.AlarmSeverityCode</t>
+          <t>Lot(구매) + LotExt.LotOriginType·VendorID·VendorLotNumber</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>② 표준 알람에 중요도 없음</t>
+          <t>공급사 LOT 번호가 품목 간 중복(75개 번호 → 169개 품목 LOT) — 로트식별자 = 공급사LOT_품목. 표준 LotType은 고정형이라 출처는 확장</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -27914,32 +28870,32 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC05 / SC07</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>erp.tb_sd_cust.cust_grp</t>
+          <t>erp.tb_sd_dlv.lot_no &lt; E260921, erp.tb_mm_stock_lot(rcv_dt &lt; 20260801)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>고객군 OE/AM</t>
+          <t>MES 도입 전·기초 재고 LOT</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>확장 속성</t>
+          <t>표준 매핑</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>CustomerPartyMasterExt.CustomerGroupCode</t>
+          <t>Lot(이관, LotOriginType LEGACY) — 출하·LOT 재고 기록으로 LOT만 등록</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>② 표준 고객사에 고객군 없음</t>
+          <t>S1 품질 이슈(MES 도입 전 LOT 고아) — 참조 무결성 확보</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -27959,32 +28915,32 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>SC04</t>
+          <t>SC04 / Q-SC04-17</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>mes.tb_alarm.alm_cd</t>
+          <t>mes.tb_alarm.alm_lvl</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>알람 코드 A001~A900</t>
+          <t>알람 중요도 H/M/L</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>코드 대응</t>
+          <t>확장 속성</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>ErrorCode(EquipmentErrorCode): A001→EQ-001, A101→EQ-003, A102·A301→EQ-004, A201→EQ-002, A900→EQ-005, A202→EQ-008(확장)</t>
+          <t>AlarmExt.AlarmSeverityCode</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>표준 회사정의 그룹 — 진동 과다만 하위 확장</t>
+          <t>② 표준 알람에 중요도 없음</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -28004,32 +28960,32 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC07</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>mes.tm_eqp.eqp_grp</t>
+          <t>erp.tb_sd_cust.cust_grp</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>설비그룹</t>
+          <t>고객군 OE/AM</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>코드 대응</t>
+          <t>확장 속성</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>EquipmentLargeClass: CNC→MCH, LKT·VIS→TST, DCM→CST·WSH→CLN·ASM→ASM·PKG→PKM(확장)</t>
+          <t>CustomerPartyMasterExt.CustomerGroupCode</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>회사정의(계층) 그룹 하위 확장</t>
+          <t>② 표준 고객사에 고객군 없음</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -28049,17 +29005,17 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC04</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>erp.tb_mm_item.item_grp</t>
+          <t>mes.tb_alarm.alm_cd</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>품목군</t>
+          <t>알람 코드 A001~A900</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -28069,12 +29025,12 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>ItemLargeClass: EWP→PRD, HSG·PRT→MEC, MTR·ELC→ELC, PKG→PKG, RAW→MTL, CSM→CSM(확장)</t>
+          <t>ErrorCode(EquipmentErrorCode): A001→EQ-001, A101→EQ-003, A102·A301→EQ-004, A201→EQ-002, A900→EQ-005, A202→EQ-008(확장)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>회사정의(계층) 그룹 하위 확장</t>
+          <t>표준 회사정의 그룹 — 진동 과다만 하위 확장</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -28094,17 +29050,17 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC01</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>erp.tb_sd_so_h.so_tp</t>
+          <t>mes.tm_eqp.eqp_grp</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>수주유형 N/S</t>
+          <t>설비그룹</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -28114,12 +29070,12 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>SalesOrderType: N·S→DOMESTIC(병합)</t>
+          <t>EquipmentLargeClass: CNC→MCH, LKT·VIS→TST, DCM→CST·WSH→CLN·ASM→ASM·PKG→PKM(확장)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>보수용 구분은 고객군(확장)으로 유지</t>
+          <t>회사정의(계층) 그룹 하위 확장</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -28139,40 +29095,130 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
+          <t>SC01</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>erp.tb_mm_item.item_grp</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>품목군</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>코드 대응</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>ItemLargeClass: EWP→PRD, HSG·PRT→MEC, MTR·ELC→ELC, PKG→PKG, RAW→MTL, CSM→CSM(확장)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>회사정의(계층) 그룹 하위 확장</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>erp.tb_sd_so_h.so_tp</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>수주유형 N/S</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>코드 대응</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>SalesOrderType: N·S→DOMESTIC(병합)</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>보수용 구분은 고객군(확장)으로 유지</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
           <t>SC03</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>mes.tm_param.unit N·m, cc/min</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>토크·누설량 단위</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>S3 처리</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>확장 단위 후보(단위그룹 확장 — ksxgen 다음 버전)</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>표준 단위코드에 없음 — 적재 시 원천 단위 문자열 보존</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
@@ -28250,7 +29296,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>오류 0, 경고 0 — 확장 명사 5, 확장 속성 테이블 16, 확장 컬럼 92, 코드 그룹 14, 코드 49, 판정 44</t>
+          <t>오류 0, 경고 0 — 확장 명사 5, 확장 속성 테이블 17, 확장 컬럼 95, 코드 그룹 15, 코드 52, 판정 46</t>
         </is>
       </c>
       <c r="D2" s="7" t="n"/>
@@ -28327,7 +29373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -28854,10 +29900,31 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>LotExt</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>CREATE TABLE ext."LotExt" ( -- 로트 확장 (확장 속성 → Lot)
+    "LotExtSequenceNo" BIGINT GENERATED BY DEFAULT AS IDENTITY, -- 로트 확장 일련번호(PK)
+    "EnterpriseID" VARCHAR(50) NOT NULL, -- 회사식별자
+    "LotID" VARCHAR(50) NOT NULL, -- 로트식별자
+    "LotOriginType" VARCHAR(30) NOT NULL, -- 로트출처유형
+    "VendorID" VARCHAR(50), -- 공급사식별자
+    "VendorLotNumber" VARCHAR(255), -- 공급사로트번호
+    CONSTRAINT "PK_LotExt" PRIMARY KEY ("LotExtSequenceNo"),
+    CONSTRAINT "UK_LotExt" UNIQUE ("EnterpriseID", "LotID")
+);</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>(물리 FK)</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>ALTER TABLE ext."StandardCost" ADD CONSTRAINT "FK_StandardCost_01" FOREIGN KEY ("EnterpriseID") REFERENCES ksx."Enterprise" ("EnterpriseID") DEFERRABLE INITIALLY IMMEDIATE;
 ALTER TABLE ext."StandardCost" ADD CONSTRAINT "FK_StandardCost_02" FOREIGN KEY ("EnterpriseID", "SiteID") REFERENCES ksx."Site" ("EnterpriseID", "SiteID") DEFERRABLE INITIALLY IMMEDIATE;
@@ -28919,7 +29986,9 @@
 ALTER TABLE ext."ProductIncomingExt" ADD CONSTRAINT "FK_ProductIncomingExt_02" FOREIGN KEY ("EnterpriseID", "ProductionOrderID", "ProductionOrderSequence") REFERENCES ksx."ProductionOrder" ("EnterpriseID", "ProductionOrderID", "ProductionOrderSequence") DEFERRABLE INITIALLY IMMEDIATE;
 ALTER TABLE ext."TraceParameterExt" ADD CONSTRAINT "FK_TraceParameterExt_01" FOREIGN KEY ("EnterpriseID", "TraceParameterID") REFERENCES ksx."TraceParameter" ("EnterpriseID", "TraceParameterID") DEFERRABLE INITIALLY IMMEDIATE;
 ALTER TABLE ext."TraceParameterExt" ADD CONSTRAINT "FK_TraceParameterExt_02" FOREIGN KEY ("EnterpriseID", "LotID") REFERENCES ksx."Lot" ("EnterpriseID", "LotID") DEFERRABLE INITIALLY IMMEDIATE;
-ALTER TABLE ext."EquipmentParameterExt" ADD CONSTRAINT "FK_EquipmentParameterExt_01" FOREIGN KEY ("EnterpriseID", "ParameterID") REFERENCES ksx."EquipmentParameter" ("EnterpriseID", "ParameterID") DEFERRABLE INITIALLY IMMEDIATE;</t>
+ALTER TABLE ext."EquipmentParameterExt" ADD CONSTRAINT "FK_EquipmentParameterExt_01" FOREIGN KEY ("EnterpriseID", "ParameterID") REFERENCES ksx."EquipmentParameter" ("EnterpriseID", "ParameterID") DEFERRABLE INITIALLY IMMEDIATE;
+ALTER TABLE ext."LotExt" ADD CONSTRAINT "FK_LotExt_01" FOREIGN KEY ("EnterpriseID", "LotID") REFERENCES ksx."Lot" ("EnterpriseID", "LotID") DEFERRABLE INITIALLY IMMEDIATE;
+ALTER TABLE ext."LotExt" ADD CONSTRAINT "FK_LotExt_02" FOREIGN KEY ("EnterpriseID", "VendorID") REFERENCES ksx."VendorPartyMaster" ("EnterpriseID", "VendorID") DEFERRABLE INITIALLY IMMEDIATE;</t>
         </is>
       </c>
     </row>
